--- a/docs/analysis/pokrytie-maskirovaniya-perechen-d8-dlya-zakazchika.xlsx
+++ b/docs/analysis/pokrytie-maskirovaniya-perechen-d8-dlya-zakazchika.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Покрытие маскирования" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Три слоя маскирования" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -120,6 +120,30 @@
       <color rgb="00A8393B"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="000E6E63"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001E7A4C"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="0093630F"/>
+      <sz val="12"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -175,7 +199,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -238,6 +262,12 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1799,162 +1829,1396 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="10" t="inlineStr">
-        <is>
-          <t>СВОДКА ПО СТАТУСАМ</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>Количество пунктов</t>
-        </is>
-      </c>
-      <c r="C3" s="11" t="inlineStr">
-        <is>
-          <t>Доля</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>Маскируется</t>
-        </is>
-      </c>
-      <c r="B4" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="14">
-        <f>B4/30</f>
-        <v>0.13333333333333333</v>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Три слоя детектирования и схема маскирования — по пунктам Перечня Д8 + общесистемные типы платформы</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="140" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Разбивка по механизму обнаружения, которым реально располагает платформа (по ответам вендора на RFI, §2.3: «обнаружение ПДн тремя механизмами — аннотации каталога метаданных, свыше 250 формальных правил для типизированных идентификаторов (для шести типов — ИНН, СНИЛС, банковская карта, ОГРН, IBAN, VIN — дополнительно проверяются контрольные соотношения; для остальных — только распознавание по формату), NER для свободного текста (только ФИО/организации/география)»; плюс собственный DLP-механизм §5.3 для контента вне PII — классификация текста + база защищаемых сведений + матрица получателей + блокировка/эскалация, механизм работает автономно). Слой 1 — распознавание по формату (regex/шаблон), без вычисляемой контрольной суммы. Слой 2 — вычисляемые значения: контрольная сумма поверх самого значения, ТОЛЬКО шесть типов из RFI. Слой 3 — нет фиксированного формата вообще (организационный/описательный текст) — детектируется не значением, а смыслом формулировки через DLP-механизм платформы, а не PIIType. Один пункт Перечня может содержать поля из разных слоёв одновременно — тогда пункт присутствует в нескольких таблицах ниже. ВАЖНО: только фактическая принадлежность к списку из RFI помечена как подтверждённый факт; всё остальное (предложенные кастомные типы, гипотезы про механизм DLP, иллюстративные формулировки) — рабочие предложения, требующие подтверждения вендором/заказчиком, помечены явно — см. столбец «Комментарий» в каждой таблице.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="24" t="inlineStr">
+        <is>
+          <t>СЛОЙ 1 — Распознавание по формату (regex/шаблон, БЕЗ вычисляемой контрольной суммы)</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
-        <is>
-          <t>Частично</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="C5" s="14">
-        <f>B5/30</f>
-        <v>0.16666666666666666</v>
+      <c r="A5" s="25" t="inlineStr">
+        <is>
+          <t>Пункт Перечня</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Что маскируем</t>
+        </is>
+      </c>
+      <c r="C5" s="25" t="inlineStr">
+        <is>
+          <t>Regex-шаблон (пример)</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>Пример совпадения</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>Надёжность</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>Тип платформы / статус</t>
+        </is>
+      </c>
+      <c r="G5" s="25" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="inlineStr">
-        <is>
-          <t>Не маскируется</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>21</v>
-      </c>
-      <c r="C6" s="14">
-        <f>B6/30</f>
-        <v>0.7</v>
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>ФИО по ключу («ФИО:», «Ф.И.О.»)</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>(?:ФИО|Ф\.?И\.?О\.?)\s*[:\-]?\s*[А-ЯЁ][а-яё]+\s[А-ЯЁ][а-яё]+(?:\s[А-ЯЁ][а-яё]+)?</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>ФИО: Смирнов Пётр Александрович</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>FULL_NAME — маскируется</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>Regex ловит ключ-значение. Свободное упоминание ФИО без ключевого слова — отдельный механизм, NER, не regex (см. примечание под таблицей)</t>
+        </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
-        <is>
-          <t>Итого пунктов</t>
-        </is>
-      </c>
-      <c r="B7" s="17" t="n">
-        <v>30</v>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Фирменное наименование клиента-юрлица</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>(?:ООО|ПАО|АО|ЗАО|ИП)\s[«\"][^»\"]{2,60}[»\"]</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>ООО «Брокер-Партнёр»</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>ORG — не выделено отдельным пунктом для клиента (есть для контрагента, п. 2.1)</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>В исходном Перечне ORG-пример относится к контрагентам (2.1), для клиента-юрлица из 1.3 действует тот же механизм (regex по организационно-правовой форме + NER на название)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Номер телефона</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>(?:\+7|8)[\s\-]?\(?\d{3}\)?[\s\-]?\d{3}[\s\-]?\d{2}[\s\-]?\d{2}</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>+7 916 123-45-67</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>PHONE — маскируется</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>ИЗ НИХ «НЕ МАСКИРУЕТСЯ» — ПО ПРИЧИНЕ</t>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Адрес электронной почты</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>[A-Za-z0-9._%+\-]+@[A-Za-z0-9.\-]+\.[A-Za-z]{2,}</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>p.smirnov.test@example.ru</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>EMAIL — маскируется</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Адрес фактического места жительства / регистрации</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>г\.?\s?[А-ЯЁ][а-яё]+.{0,60}?(?:ул\.|улица|пр-т|проспект|д\.|дом).{0,30}</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>г. Москва, ул. Тестовая, д. 12, кв. 5</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>ADDRESS — маскируется</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="inlineStr">
+        <is>
+          <t>Формат-эвристика, не строгий regex: структура адреса вариативна, реальный детектор ближе к NER+словарь географических названий, чем к одному шаблону</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Паспорт РФ — серия и номер</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>\d{2}\s?\d{2}\s?\d{6}</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>4510 123456</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>PASSPORT — частично (только паспорт РФ)</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Контрольной суммы у номера паспорта РФ нет — это слой 1, не слой 2. Без привязки к ключевому слову рядом («паспорт», «серия») любые 10 цифр подряд (кусок счёта/телефона) дадут ложное срабатывание — на практике нужен контекстный якорь, как у даты рождения ниже</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Место выдачи паспорта</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>(?:выдан|код подразделения)\s*[:\-]?\s*.{5,80}</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>выдан ОВД района Хамовники г. Москвы</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>не выделено отдельным PIIType</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="inlineStr">
+        <is>
+          <t>Ключ-значение эвристика, высокий риск ложных срабатываний без ключевого слова рядом</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>1.2 / 1.3</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Дата рождения (в связке с ключевым словом)</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>(?:дата рождения|д\.р\.)\s*[:\-]?\s*\d{2}\.\d{2}\.\d{4}</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>дата рождения: 14.03.1985</t>
+        </is>
+      </c>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>DOB — формальное правило платформы (RFI, §2.3), не выделено отдельным пунктом Перечня явно</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>Без ключевого слова рядом — слишком много ложных срабатываний на любые даты в документе</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Банковский счёт (20 цифр)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>\d{20}</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>40817810900001234567</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Средняя</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>BANK_ACCOUNT — формальное правило платформы (RFI, §2.3)</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="inlineStr">
+        <is>
+          <t>RFI прямо называет шестью checksum-типами ИНН/СНИЛС/карту/ОГРН/IBAN/VIN, банковский счёт — в списке «остальных, распознаваемых по формату». Реальный алгоритм ЦБ РФ для счёта существует (веса 7,1,3 по разрядам БИК+счёта), но RFI не подтверждает, что платформа его применяет — поэтому здесь, не в слое 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>IP-адрес</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>\b(?:\d{1,3}\.){3}\d{1,3}(?:/\d{1,2})?\b</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>10.10.1.0/24</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>Высокая</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>IP — маскируется (частично, см. п. 3.3)</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>Тип IP уже встроен в платформу</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Имя сервера / хостнейм (предлагается)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>[a-z0-9]([a-z0-9\-]{0,61}[a-z0-9])?\.(?:local|internal|corp)\b</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>itq-db-01.internal</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>не входит во встроенные типы — предложение</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Не подтверждено вендором. Открытый вопрос заказчику: подтвердить домен внутренней сети, чтобы не ловить произвольные слова с точкой</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Номер договора (предлагается, кастомный тип)</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>№?\s?[А-ЯA-Z]{2,10}(?:[\-/][A-Za-zА-я0-9]+){1,5}</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>ИКД-1-PRO-TEST-001</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>не входит во встроенные типы — предложение</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Не подтверждено вендором — предложение, требующее проверки. Контрольной суммы нет; формат у разных подразделений заказчика не подтверждён</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Уникальный код клиента (предлагается)</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>CL[\-_]?\d{4,8}</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>CL-000482</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Низкая</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>не входит во встроенные типы — предложение</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Не подтверждено вендором. Формат гипотетический, реальный шаблон кода клиента у заказчика не подтверждён</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="26" t="inlineStr">
+        <is>
+          <t>СЛОЙ 2 — Вычисляемые значения (контрольная сумма — ТОЛЬКО 6 типов, подтверждённых RFI)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="48" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Ни один из этих типов не назван в Перечне Д8 буквально — RFI подтверждает контрольную сумму ровно для шести типов (ИНН, СНИЛС, банковская карта, ОГРН, IBAN, VIN), они добавлены здесь для полноты технической картины и как контекст: часть из них используется в тестовых данных пилота, часть релевантна отдельным пунктам Перечня по смыслу (см. столбец «Связь с Перечнем»). VIN (транспортные средства) в таблицу не включён — неприменим ни к одному пункту Перечня Д8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="25" t="inlineStr">
+        <is>
+          <t>Связь с Перечнем</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Что маскируем</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="inlineStr">
+        <is>
+          <t>Алгоритм проверки</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>Пример</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="inlineStr">
+        <is>
+          <t>Тип платформы / статус</t>
+        </is>
+      </c>
+      <c r="F22" s="25" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>не названо в Перечне буквально</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>ИНН физлица (12 цифр)</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Контрольная цифра 11: (7,2,4,10,3,5,9,4,6,8) · (d1…d10), сумма mod 11, затем mod 10. Контрольная цифра 12: (3,7,2,4,10,3,5,9,4,6,8) · (d1…d11), аналогично mod 11 mod 10</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>770912345616</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>INN — подтверждено RFI (§2.3, один из 6 checksum-типов)</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Алгоритм регулирует ФНС. Веса выше соответствуют официальному алгоритму ФНС</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>1.2 (по смыслу, «данные документов»)</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>СНИЛС</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Сумма (цифра × вес, вес 9→1 по первым 9 цифрам) по модулю 101; если сумма &lt; 100 — контрольное число равно самой сумме; если сумма = 100 или 101 — контрольное число «00»</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>123-456-789 64</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>SNILS — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Не выделен отдельным пунктом Перечня — входит в «данные документов, удостоверяющих личность» по смыслу, требует подтверждения у заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>не в Перечне (общесистемный тип)</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Банковская карта</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Алгоритм Луна: справа налево удваивать каждую вторую цифру, если результат ≥10 — вычесть 9, сумма всех цифр должна делиться на 10 без остатка</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>4111 1111 1111 1111</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>BANK_CARD — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Пример — стандартный тестовый номер карты, реально проходящий проверку алгоритмом Луна</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>2.1 (если код контрагента = ОГРН)</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>ОГРН / ОГРНИП</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>ОГРН (13 цифр): 13-й разряд = (первые 12 цифр mod 11) mod 10. ОГРНИП (15 цифр): аналогично по модулю 13</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>1027700123450</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>OGRN — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Релевантно, если «уникальный код» контрагента/юрлица в п. 2.1 фактически ОГРН — требует подтверждения у заказчика</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>1.5 (если расчёты через зарубежный счёт)</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>IBAN</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Контрольная сумма ISO 7064 (mod 97): переставить первые 4 символа в конец, буквы → цифры (A=10…Z=35), остаток от деления на 97 должен быть равен 1</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>DE89 3704 0044 0532 0130 00</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>IBAN — подтверждено RFI (§2.3)</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Релевантно для п. 1.5 «поручения на покупку/продажу иностранной валюты», если расчёты идут через зарубежный счёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
+        <is>
+          <t>СЛОЙ 3 — Примеры формулировок для DLP (нет фиксированного значения, только смысл)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="76" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>⚠ Слой с наименьшей надёжностью из трёх. RFI (§5.3) подтверждает только сам факт наличия у платформы механизма «классификация текста + база защищаемых сведений» — конкретный метод (ключевые слова/фразы, как условно показано ниже, или более устойчивая семантическая модель) вендором не детализирован; формулировка «DLP по ключевым фразам» в таблице — рабочая гипотеза, не факт из RFI. Ключевой практический риск: поиск по ключевым словам/фразам обходится перефразированием, синонимами, англицизмами (например «NDA» вместо «соглашение о неразглашении») и опечатками — то есть это в принципе менее надёжный слой, чем 1 и 2, и должен быть проверен на реальных документах Д8 в ходе пилота, а не воспринят как готовое покрытие. Все формулировки ниже, кроме п. 1.1 (пример самого заказчика), — иллюстративные примеры, не выдержки из реальных документов Д8.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Пункт Перечня</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
-        <is>
-          <t>Кол-во пунктов</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
-        <is>
-          <t>Доля от 30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="19" t="inlineStr">
-        <is>
-          <t>Возможен отдельный тип для маскирования (финансово-операционные детали, п. 1.3–1.5)</t>
-        </is>
-      </c>
-      <c r="B12" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" s="21">
-        <f>B12/30</f>
-        <v>0.26666666666666666</v>
-      </c>
-    </row>
-    <row r="13" ht="34" customHeight="1">
-      <c r="A13" s="22" t="inlineStr">
-        <is>
-          <t>Другой слой контроля — не персональные данные (IT/ИБ/политика ИИ/договорная информация)</t>
-        </is>
-      </c>
-      <c r="B13" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="C13" s="21">
-        <f>B13/30</f>
-        <v>0.43333333333333335</v>
-      </c>
-    </row>
-    <row r="16" ht="92" customHeight="1">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Пункты «Не маскируется» относятся к двум разным по природе группам. 8 пунктов раздела 1 (номера/даты договоров, сделки по счетам, займы, задолженность, прекращённые обязательства, остатки, поручения) — финансово-операционные детали, для которых можно предложить отдельный тип для маскирования. 13 пунктов (контрагентские соглашения, IT-инфраструктура, меры ИБ, программный код, политика работы с ИИ) — не персональные данные, требуют другого слоя контроля. Для второй группы у платформы есть встроенный механизм контроля передачи текста (см. примечание на листе «Покрытие маскирования»). По каждому пункту в столбце «Вопрос к заказчику» — уточняющий вопрос с примером и, где применимо, наша рекомендация.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="46" customHeight="1">
-      <c r="A18" s="23" t="inlineStr">
-        <is>
-          <t>Отдельный момент по срокам: пункт 1.3 «Номера и даты договоров» уже используется как целевой показатель в критерии приёмки пилота — до получения вашего ответа по этому пункту приёмочный тест может не набрать нужный процент именно из-за этого пробела. Просим уделить ему приоритетное внимание.</t>
+      <c r="C31" s="25" t="inlineStr">
+        <is>
+          <t>Пример формулировки (что ищем)</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>Как предлагаем скрывать</t>
+        </is>
+      </c>
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Индивидуальные схемы обслуживания</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>«Обслуживание по индивидуальному тарифному плану с персональным менеджером», «особые условия обслуживания счёта клиента»</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>DLP-механизм платформы (§5.3): база защищаемых сведений + блокировка/эскалация</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>Единственный пример, сформулированный самим заказчиком в исходном запросе (лист «Покрытие маскирования»)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Роль представителя/бенефициара (не само ФИО)</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>«выгодоприобретатель — …», «бенефициарный владелец — …, доля 40%»</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «выгодоприобретатель», «бенефициар», «представитель» (гипотеза механизма — см. примечание ниже)</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>ФИО в этой же фразе покрывается отдельно (слой 1/NER), здесь — только роль/связь. Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Содержание сделки (актив, объём — без суммы)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>«совершена сделка на покупку 100 акций Сбербанк»</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>DLP по паттерну «сделка на покупку/продажу [актив]»; сумма сделки — отдельно слой 1 (денежный формат)</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>Составной случай: сумма и номер счёта уже маскируются, содержание сделки как категория — нет. Иллюстративный пример</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Маржинальные займы (условия)</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>«предоставлен маржинальный заём в размере … под …% годовых»</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевой фразе «маржинальный заём»; сумма — слой 1</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Задолженность (факт)</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>«задолженность клиента составляет …», «просроченная задолженность по счёту»</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевой фразе «задолженность»; сумма — слой 1</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Прекращённые/неисполненные обязательства</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>«обязательство … признано прекращённым/не исполненным»</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «обязательство прекращено», «не исполнено»; номер сделки — слой 1 (regex)</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>1.3</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Исходящий остаток по активу</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>«исходящий остаток по счёту: 500 акций Газпром, плановый остаток — 480 акций»</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевой фразе «исходящий остаток»</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>Открытый вопрос: считать ли остаток конфиденциальным без привязки к ФИО в той же фразе</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>1.4</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Поручение на сделку с финансовым инструментом (документ целиком)</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>«поручение клиента на покупку/продажу [инструмент] на сумму …»</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Блокировка документа целиком по классу «поручение», а не построчное маскирование</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Вложенные ФИО/суммы покрываются отдельно; сам факт/тип поручения — только через DLP-классификацию документа</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Поручение на валютную операцию (документ целиком)</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>«поручение на продажу 10 000 USD по курсу 92,50»</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Аналогично п. 1.4 — блокировка документа/DLP-классификация</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2.1</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Информация о взаимоотношениях с контрагентом</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>«по договору с контрагентом ООО «…» установлены следующие условия…»</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «условия договора», «взаимоотношения с контрагентом»; название юрлица — отдельно NER (ORG)</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2.2</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Условия партнёрских программ</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>«комиссия по агентскому соглашению составляет 0,15% от объёма сделок»</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «агентское соглашение», «партнёрская программа»</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>3.1</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Система разграничения доступа (описание)</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>«доступ к модулю «Клиентские счета» имеют роли: Операционист, Старший операционист»</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Не PII вообще — предлагается закрывать оргмерами/RBAC, а не DLP-детектором текста</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>Формально слой 3 по запросу проработать пример для каждого пункта, но по сути это вне PII-маскировщика в принципе</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Права доступа сотрудников</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>«сотруднику … предоставлен доступ уровня «Администратор» к CRM»</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Аналогично п. 3.1 — оргмеры/RBAC, не DLP по тексту</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>ФИО сотрудника в этой же фразе покрывается отдельно</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Топология/схема сети (текстовое описание, не сами IP)</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>«схема сети: DMZ → firewall → внутренний сегмент, сервер …»</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «схема сети», «DMZ», «сегмент сети»; IP-адреса и хостнеймы — отдельно слой 1</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>Программный код</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Синтаксические признаки кода (отступы, скобки, ключевые слова языка), не текстовая формулировка</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Не поддерживается ни один из трёх слоёв — предлагается блокировка по расширению/MIME-типу файла на входном шлюзе до индексации/отправки в ИИ</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Список поддерживаемых форматов платформы (PDF/DOCX/DOC/TXT/MD/CSV/XLSX/JSON/XML) не включает файлы кода, это технически упрощает блокировку на входе, а не через анализ содержимого</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>4.1</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>Методы/способы защиты информации</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>«используется двухфакторная аутентификация и шифрование AES-256»</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам названий методов защиты</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>Меры безопасности персонала</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>«сотрудники проходят проверку службой безопасности, подписывают NDA»</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым фразам «проверка службой безопасности», «NDA»</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Меры по критической инфраструктуре</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>«резервный дата-центр расположен по адресу …, время переключения 15 минут»</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Адрес объекта — слой 1 (эвристика ADDRESS/LOC); технические параметры (время переключения) — DLP по ключевым словам</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Названия/модели средств защиты</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>«установлена система видеонаблюдения Hikvision DS-2CD2, СКУД Perco»</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>DLP по словарю моделей оборудования (список, не regex — названия непредсказуемо разнообразны)</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Охрана / пропускной режим</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>«турникеты на 1 этаже, пост охраны круглосуточно»</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «пропускной режим», «пост охраны»</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Результаты проверок/аудитов/пентестов</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>«по итогам пентеста выявлено 3 уязвимости критического уровня»</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>DLP по ключевым словам «пентест», «аудит», «уязвимость»</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>Иллюстративный пример, не из реального документа Д8</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="44" customHeight="1">
+      <c r="A54" s="9" t="inlineStr">
+        <is>
+          <t>П. 5.1 и 5.2 Перечня («материалы для ИИ» / «результаты ИИ», если содержат сведения из разделов 1–4) намеренно не включены в таблицу выше строкой: это не текстовая формулировка для поиска, а зонтичное правило агрегации результатов остальных слоёв («заблокировать документ/ответ, если сработал любой из слоёв 1–3 на контенте из разделов 1–4»).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="70" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
+        <is>
+          <t>Примечание про ФИО и организации: свободное упоминание имени/организации в связном тексте (не по ключу «ФИО:») распознаётся не регулярным выражением, а NER-моделью (третий из трёх официальных механизмов детектирования платформы, см. RFI §2.3) — отдельный способ обнаружения, который не укладывается ровно ни в один из трёх запрошенных слоёв. В таблицах выше он условно отнесён к слою 1 там, где встречается по ключевому слову (regex-обвязка вокруг NER-результата); свободные упоминания ФИО/организаций в тексте документа технически ближе к слою 3 по механизму (не по формату значения, а по контексту).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A18:C18"/>
+  <mergeCells count="9">
+    <mergeCell ref="A29:I29"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A56:I56"/>
+    <mergeCell ref="A30:I30"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A54:I54"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
